--- a/core/public/file/FileExcelPhieuNhap.xlsx
+++ b/core/public/file/FileExcelPhieuNhap.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="20">
   <si>
     <t>Mã phiếu</t>
   </si>
@@ -86,18 +86,31 @@
   </si>
   <si>
     <t>đây là ghi chú</t>
+  </si>
+  <si>
+    <t>Thành tiền</t>
+  </si>
+  <si>
+    <t>Giá bán</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -127,22 +140,44 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="6">
+  <dxfs count="8">
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <numFmt numFmtId="30" formatCode="@"/>
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -154,10 +189,6 @@
     <dxf>
       <numFmt numFmtId="30" formatCode="@"/>
       <alignment horizontal="left"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="30" formatCode="@"/>
@@ -181,16 +212,18 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="tableTable" displayName="tableTable" ref="A1:G20" totalsRowShown="0">
-  <autoFilter ref="A1:G20"/>
-  <tableColumns count="7">
-    <tableColumn id="1" name="Mã phiếu" dataDxfId="5"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="tableTable" displayName="tableTable" ref="A1:I20" totalsRowShown="0">
+  <autoFilter ref="A1:I20"/>
+  <tableColumns count="9">
+    <tableColumn id="1" name="Mã phiếu" dataDxfId="7"/>
     <tableColumn id="7" name="Ngày nhập"/>
-    <tableColumn id="2" name="Mã sản phẩm" dataDxfId="4"/>
-    <tableColumn id="4" name="Số lượng" dataDxfId="3"/>
-    <tableColumn id="5" name="Mã nhà cung cấp" dataDxfId="2"/>
-    <tableColumn id="9" name="Mã kho" dataDxfId="1"/>
-    <tableColumn id="8" name="Ghi chú" dataDxfId="0"/>
+    <tableColumn id="2" name="Mã sản phẩm" dataDxfId="6"/>
+    <tableColumn id="6" name="Giá bán" dataDxfId="2"/>
+    <tableColumn id="4" name="Số lượng" dataDxfId="1"/>
+    <tableColumn id="3" name="Thành tiền" dataDxfId="0"/>
+    <tableColumn id="5" name="Mã nhà cung cấp" dataDxfId="5"/>
+    <tableColumn id="9" name="Mã kho" dataDxfId="4"/>
+    <tableColumn id="8" name="Ghi chú" dataDxfId="3"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -483,15 +516,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="4" width="21" customWidth="1"/>
-    <col min="5" max="7" width="35.5703125" customWidth="1"/>
+    <col min="2" max="3" width="21" customWidth="1"/>
+    <col min="4" max="6" width="21" style="6" customWidth="1"/>
+    <col min="7" max="9" width="35.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="1" customFormat="1">
+    <row r="1" spans="1:9" s="1" customFormat="1">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -501,20 +535,26 @@
       <c r="C1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:9">
       <c r="A2" s="3" t="s">
         <v>2</v>
       </c>
@@ -524,18 +564,25 @@
       <c r="C2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="4">
+        <v>1000</v>
+      </c>
+      <c r="E2" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="F2" s="7">
+        <f>D2 * E2</f>
+        <v>10000</v>
+      </c>
+      <c r="G2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="H2" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="G2" s="3"/>
-    </row>
-    <row r="3" spans="1:7">
+      <c r="I2" s="3"/>
+    </row>
+    <row r="3" spans="1:9">
       <c r="A3" s="3" t="s">
         <v>3</v>
       </c>
@@ -545,177 +592,218 @@
       <c r="C3" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="4">
+        <v>1000</v>
+      </c>
+      <c r="E3" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="F3" s="7">
+        <f>D3 * E3</f>
+        <v>10000</v>
+      </c>
+      <c r="G3" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="H3" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="I3" s="3" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:9">
       <c r="A4" s="3"/>
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
       <c r="G4" s="3"/>
-    </row>
-    <row r="5" spans="1:7">
+      <c r="H4" s="3"/>
+      <c r="I4" s="3"/>
+    </row>
+    <row r="5" spans="1:9">
       <c r="A5" s="3"/>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
       <c r="G5" s="3"/>
-    </row>
-    <row r="6" spans="1:7">
+      <c r="H5" s="3"/>
+      <c r="I5" s="3"/>
+    </row>
+    <row r="6" spans="1:9">
       <c r="A6" s="3"/>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
       <c r="G6" s="3"/>
-    </row>
-    <row r="7" spans="1:7">
+      <c r="H6" s="3"/>
+      <c r="I6" s="3"/>
+    </row>
+    <row r="7" spans="1:9">
       <c r="A7" s="3"/>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
       <c r="G7" s="3"/>
-    </row>
-    <row r="8" spans="1:7">
+      <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
+    </row>
+    <row r="8" spans="1:9">
       <c r="A8" s="3"/>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4"/>
       <c r="G8" s="3"/>
-    </row>
-    <row r="9" spans="1:7">
+      <c r="H8" s="3"/>
+      <c r="I8" s="3"/>
+    </row>
+    <row r="9" spans="1:9">
       <c r="A9" s="3"/>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4"/>
+      <c r="F9" s="4"/>
       <c r="G9" s="3"/>
-    </row>
-    <row r="10" spans="1:7">
+      <c r="H9" s="3"/>
+      <c r="I9" s="3"/>
+    </row>
+    <row r="10" spans="1:9">
       <c r="A10" s="3"/>
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4"/>
+      <c r="F10" s="4"/>
       <c r="G10" s="3"/>
-    </row>
-    <row r="11" spans="1:7">
+      <c r="H10" s="3"/>
+      <c r="I10" s="3"/>
+    </row>
+    <row r="11" spans="1:9">
       <c r="A11" s="3"/>
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="4"/>
+      <c r="F11" s="4"/>
       <c r="G11" s="3"/>
-    </row>
-    <row r="12" spans="1:7">
+      <c r="H11" s="3"/>
+      <c r="I11" s="3"/>
+    </row>
+    <row r="12" spans="1:9">
       <c r="A12" s="3"/>
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
+      <c r="D12" s="4"/>
+      <c r="E12" s="4"/>
+      <c r="F12" s="4"/>
       <c r="G12" s="3"/>
-    </row>
-    <row r="13" spans="1:7">
+      <c r="H12" s="3"/>
+      <c r="I12" s="3"/>
+    </row>
+    <row r="13" spans="1:9">
       <c r="A13" s="3"/>
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
+      <c r="D13" s="4"/>
+      <c r="E13" s="4"/>
+      <c r="F13" s="4"/>
       <c r="G13" s="3"/>
-    </row>
-    <row r="14" spans="1:7">
+      <c r="H13" s="3"/>
+      <c r="I13" s="3"/>
+    </row>
+    <row r="14" spans="1:9">
       <c r="A14" s="3"/>
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
+      <c r="D14" s="4"/>
+      <c r="E14" s="4"/>
+      <c r="F14" s="4"/>
       <c r="G14" s="3"/>
-    </row>
-    <row r="15" spans="1:7">
+      <c r="H14" s="3"/>
+      <c r="I14" s="3"/>
+    </row>
+    <row r="15" spans="1:9">
       <c r="A15" s="3"/>
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
+      <c r="D15" s="4"/>
+      <c r="E15" s="4"/>
+      <c r="F15" s="4"/>
       <c r="G15" s="3"/>
-    </row>
-    <row r="16" spans="1:7">
+      <c r="H15" s="3"/>
+      <c r="I15" s="3"/>
+    </row>
+    <row r="16" spans="1:9">
       <c r="A16" s="3"/>
       <c r="B16" s="3"/>
       <c r="C16" s="3"/>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
+      <c r="D16" s="4"/>
+      <c r="E16" s="4"/>
+      <c r="F16" s="4"/>
       <c r="G16" s="3"/>
-    </row>
-    <row r="17" spans="1:7">
+      <c r="H16" s="3"/>
+      <c r="I16" s="3"/>
+    </row>
+    <row r="17" spans="1:9">
       <c r="A17" s="3"/>
       <c r="B17" s="3"/>
       <c r="C17" s="3"/>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
+      <c r="D17" s="4"/>
+      <c r="E17" s="4"/>
+      <c r="F17" s="4"/>
       <c r="G17" s="3"/>
-    </row>
-    <row r="18" spans="1:7">
+      <c r="H17" s="3"/>
+      <c r="I17" s="3"/>
+    </row>
+    <row r="18" spans="1:9">
       <c r="A18" s="3"/>
       <c r="B18" s="3"/>
       <c r="C18" s="3"/>
-      <c r="D18" s="3"/>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3"/>
+      <c r="D18" s="4"/>
+      <c r="E18" s="4"/>
+      <c r="F18" s="4"/>
       <c r="G18" s="3"/>
-    </row>
-    <row r="19" spans="1:7">
+      <c r="H18" s="3"/>
+      <c r="I18" s="3"/>
+    </row>
+    <row r="19" spans="1:9">
       <c r="A19" s="3"/>
       <c r="B19" s="3"/>
       <c r="C19" s="3"/>
-      <c r="D19" s="3"/>
-      <c r="E19" s="3"/>
-      <c r="F19" s="3"/>
+      <c r="D19" s="4"/>
+      <c r="E19" s="4"/>
+      <c r="F19" s="4"/>
       <c r="G19" s="3"/>
-    </row>
-    <row r="20" spans="1:7">
+      <c r="H19" s="3"/>
+      <c r="I19" s="3"/>
+    </row>
+    <row r="20" spans="1:9">
       <c r="A20" s="3"/>
       <c r="B20" s="3"/>
       <c r="C20" s="3"/>
-      <c r="D20" s="3"/>
-      <c r="E20" s="3"/>
-      <c r="F20" s="3"/>
+      <c r="D20" s="4"/>
+      <c r="E20" s="4"/>
+      <c r="F20" s="4"/>
       <c r="G20" s="3"/>
+      <c r="H20" s="3"/>
+      <c r="I20" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>